--- a/www/flightdata/xlsx/eoss-306.xlsx
+++ b/www/flightdata/xlsx/eoss-306.xlsx
@@ -3708,7 +3708,7 @@
         <v>27361.9</v>
       </c>
       <c r="I2">
-        <v>665</v>
+        <v>481</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
